--- a/data/워크숍.xlsx
+++ b/data/워크숍.xlsx
@@ -4,13 +4,14 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="준비업무" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="물품준비" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="당일타임라인" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="간트차트" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TF·R&amp;R" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="준비업무" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="물품준비" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="당일타임라인" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="간트차트" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,8 +55,31 @@
       <name val="Arial"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -77,8 +101,13 @@
         <fgColor rgb="0015A06A"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -114,11 +143,69 @@
         <color rgb="00E6EAF0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -143,6 +230,30 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -506,6 +617,735 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>KIMM–DLR 국제공동워크숍 준비 TF · 업무분배(R&amp;R)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>행사 2026. 8. 5.(수) 10:00–16:00 · 한국기계연구원 S1동 회의실   |   작성 2026-06-26 · 분야별 책임제</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>□ TF 구성 (실무자 4인)</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="n"/>
+      <c r="C4" s="20" t="n"/>
+      <c r="D4" s="20" t="n"/>
+      <c r="E4" s="21" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>이니셜</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>성명</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>담당 분야</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>백업</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>DW</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>강도원</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>간사·운영총괄</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>행사 기획·문서 / 인쇄물 / 비용 처리 / 최종 점검</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>전원</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>MK</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>민경욱</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>의전·손님(DLR)</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>의전·영접 / 중식 / 기념품 / 사진·기록</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>DW</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>KJ</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>김재현</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>발표·랩투어</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>발표자료 / 랩투어</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>DW</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>박진영</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>시설·물품</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>회의실·세팅 / 명찰·국기 / 물품준비</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>DW</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>□ 분야별 R&amp;R (준비 단계)</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="n"/>
+      <c r="C11" s="20" t="n"/>
+      <c r="D11" s="20" t="n"/>
+      <c r="E11" s="21" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>분야</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>담당</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>주요 업무</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>시기(마감)</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>협업</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>행사 기획·문서</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>강도원(DW)</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>세부일정·발표자·참석자 명단·예산 확정, 내부결재 기안</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>~7/17</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>전원</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>인쇄물</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>강도원(DW)</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>플랜카드·탁상 입간판 문구→디자인 의뢰(마이스피플)→인쇄·수령</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>~7/29</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>박진영</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>비용 처리</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>강도원(DW)</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>인쇄·기념품·다과·중식·회의비 정산 및 결재</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>8/6~8/14</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>최종 점검</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>강도원(DW)</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>전일(8/4) 전체 세팅·리허설 일괄 점검(체크리스트)</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>8/4</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>전원</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>발표자료</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>김재현(KJ)</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>총괄·기계연 1~3세부·DLR 발표본 취합(영문)·통합본·호환테스트</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>~8/4</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>박진영(AV)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>랩투어</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>김재현(KJ)</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>실험실 4곳 담당자 협의·영문 설명·안전·통역·이동동선</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>~7/31</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>강도원</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>의전·영접</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>민경욱(MK)</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>DLR 숙소 안내·방문자 출입/주차 등록·원내 안내표지</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>~8/4</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>중식</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>민경욱(MK)</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>식당 예약/케이터링·식이제한(채식·할랄·알레르기)·동선</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>~8/4</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>기념품·선물</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>민경욱(MK)</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>DLR 참석자용 기념품 확보(명단 확정 후)</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>~7/24</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>강도원</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>사진·기록</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>민경욱(MK)</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>촬영 담당 지정·단체사진 위치(11:50~12:00)·기록 정리</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>8/1~8/5</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>회의실·세팅</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>박진영(PJ)</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>S1동 예약·좌석배치·빔/음향/포인터·다과 세팅</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>~8/4</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>김재현(AV)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>명찰·국기</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>박진영(PJ)</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>명찰·명찰줄 디자인/인쇄·한국/독일 국기·받침대</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>~7/29</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>강도원(명단)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>□ 당일(8/5) 운영 분장</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="n"/>
+      <c r="C26" s="20" t="n"/>
+      <c r="D26" s="20" t="n"/>
+      <c r="E26" s="21" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>시간/구분</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>담당</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr"/>
+      <c r="E27" s="16" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>전체 진행·사회</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>강도원(DW)</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>식순 진행·인사말/발표 사회·시간 관리</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="21" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>발표 운영</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>김재현(KJ)</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>발표 순서·자료 송출·발표자 안내(총괄→기계연→DLR)</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="n"/>
+      <c r="E29" s="21" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>AV·회의실</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>박진영(PJ)</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="inlineStr">
+        <is>
+          <t>빔/음향/포인터 운용·좌석/명패/다과·돌발 대응</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="n"/>
+      <c r="E30" s="21" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>DLR 의전·통역</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>민경욱(MK)</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>손님 영접·동선·통역 연결·중식 안내</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="n"/>
+      <c r="E31" s="21" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>랩투어 인솔</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>김재현(KJ)</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="inlineStr">
+        <is>
+          <t>13:30~14:50 4개 실험실 인솔·안전·시간 관리</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="n"/>
+      <c r="E32" s="21" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>촬영·기록</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>민경욱(MK)</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>단체촬영(11:50)·행사 기록</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="n"/>
+      <c r="E33" s="21" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>기념품·마무리</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>강도원·민경욱</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>폐회(16:00)·기념품 전달</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="n"/>
+      <c r="E34" s="21" t="n"/>
+    </row>
+    <row r="36" ht="44" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>※ 이니셜 범례: DW=강도원, MK=민경욱, KJ=김재현, PJ=박진영. 기존 '준비업무'·'간트차트' 탭의 담당 표기(특히 DK)는 본 R&amp;R 기준으로 재정렬 필요. 분야별 마감은 준비업무 탭 일정 기준(변경 가능).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="C32:E32"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I33"/>
@@ -1774,7 +2614,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2244,13 +3084,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2300,7 +3140,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>원장님 티타임 / 기술교류회</t>
+          <t>원장님 티타임</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -2308,7 +3148,7 @@
           <t>다과 세팅, 원장 비서실</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2326,8 +3166,8 @@
           <t>참석자 소개</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2345,8 +3185,8 @@
           <t>KIMM 총괄책임자 인사말</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -2369,12 +3209,12 @@
           <t>자료 사전 점검</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10:40–11:20</t>
+          <t>10:40–11:10</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -2384,108 +3224,104 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>기계연 1~4세부 과제 발표 (각 10분)</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr"/>
+          <t>기계연 1~3세부 과제 발표 (각 10분)</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>11:20–11:50</t>
+          <t>11:10–11:20</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>발표</t>
+          <t>휴식</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>DLR 1~3세부 과제 발표 (각 10분)</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>영문 자료</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
+          <t>휴식</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>11:50–12:00</t>
+          <t>11:20–11:50</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>마무리</t>
+          <t>발표</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>'26년 일정 협의 및 기념 촬영</t>
+          <t>DLR 1~3세부 과제 발표 (각 10분)</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>단체사진 위치 사전확인</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr"/>
+          <t>영문 자료</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12:00–13:30</t>
+          <t>11:50–12:00</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>중식</t>
+          <t>마무리</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>점심 식사 (이동시간 포함)</t>
+          <t>'26년 일정 협의 및 기념 촬영</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>식당 예약·식이제한</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr"/>
+          <t>단체사진 위치 사전확인</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>13:30–13:50</t>
+          <t>12:00–13:30</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>랩투어</t>
+          <t>중식</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>가스터빈 연소기 실험실</t>
+          <t>점심 식사 (이동시간 포함)</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>담당자·안전·통역</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr"/>
+          <t>식당 예약·식이제한</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>13:50–14:10</t>
+          <t>13:30–13:50</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -2495,7 +3331,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>고온 수전해/연료전지 실험실</t>
+          <t>무탄소발전연구실 (가스터빈 연소기)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -2503,12 +3339,12 @@
           <t>담당자·안전·통역</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>14:10–14:30</t>
+          <t>13:50–14:10</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -2518,24 +3354,20 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>실험실 (미정 — 확정 필요)</t>
+          <t>무탄소발전연구실 (고온 수전해/연료전지)</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>확정 필요</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
-      </c>
+          <t>담당자·안전·통역</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>14:30–14:50</t>
+          <t>14:10–14:30</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -2545,54 +3377,111 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>실험실 (미정 — 확정 필요)</t>
+          <t>액체수소플랜트연구센터</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>확정 필요</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>⚠</t>
-        </is>
-      </c>
+          <t>담당자·안전·통역</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>14:30–14:50</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>랩투어</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>친환경모빌리티연구실</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>담당자·안전·통역</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>14:50–15:00</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>휴식</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>휴식</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>15:00–16:00</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>기술교류회</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>기술교류회</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>16:00–</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>마무리</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>마무리 및 폐회 (이동시간 포함)</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>마무리 및 폐회</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>기념품 전달</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="B2:B100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"티타임,오프닝,발표,중식,랩투어,마무리"</formula1>
+      <formula1>"티타임,오프닝,발표,휴식,중식,랩투어,기술교류회,마무리"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/data/워크숍.xlsx
+++ b/data/워크숍.xlsx
@@ -79,7 +79,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -104,6 +104,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B3741A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007A4FD0"/>
       </patternFill>
     </fill>
   </fills>
@@ -205,7 +215,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -254,6 +264,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1537,7 +1549,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1578,7 +1590,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1619,7 +1631,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1656,7 +1668,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1693,7 +1705,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>KJ</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1726,7 +1738,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>KJ</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1763,7 +1775,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>KJ</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1800,7 +1812,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>KJ</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1837,7 +1849,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>DW, DK</t>
+          <t>DW</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1915,7 +1927,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>DW, DK</t>
+          <t>DW</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1985,7 +1997,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2022,7 +2034,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2059,7 +2071,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2092,7 +2104,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>MK</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2133,7 +2145,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>MK</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2174,7 +2186,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>MK</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2219,7 +2231,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>MK</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2256,7 +2268,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>MK, DW</t>
+          <t>KJ</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2293,7 +2305,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>KJ</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -2330,7 +2342,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>KJ</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2367,7 +2379,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>MK</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -2408,7 +2420,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>MK</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -2445,7 +2457,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>MK</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -2478,7 +2490,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>MK</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2515,7 +2527,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>MK</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2589,7 +2601,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>DW, MK, DK</t>
+          <t>DW</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -3677,7 +3689,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -3686,8 +3698,8 @@
         </is>
       </c>
       <c r="E6" s="10" t="n"/>
-      <c r="F6" s="9" t="n"/>
-      <c r="G6" s="9" t="n"/>
+      <c r="F6" s="22" t="n"/>
+      <c r="G6" s="22" t="n"/>
       <c r="H6" s="10" t="n"/>
       <c r="I6" s="10" t="n"/>
       <c r="J6" s="10" t="n"/>
@@ -3704,7 +3716,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -3719,7 +3731,7 @@
       <c r="I7" s="10" t="n"/>
       <c r="J7" s="10" t="n"/>
       <c r="K7" s="10" t="n"/>
-      <c r="L7" s="9" t="n"/>
+      <c r="L7" s="22" t="n"/>
       <c r="M7" s="10" t="n"/>
     </row>
     <row r="8">
@@ -3731,7 +3743,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -3744,8 +3756,8 @@
       <c r="G8" s="10" t="n"/>
       <c r="H8" s="10" t="n"/>
       <c r="I8" s="10" t="n"/>
-      <c r="J8" s="9" t="n"/>
-      <c r="K8" s="9" t="n"/>
+      <c r="J8" s="22" t="n"/>
+      <c r="K8" s="22" t="n"/>
       <c r="L8" s="10" t="n"/>
       <c r="M8" s="10" t="n"/>
     </row>
@@ -3758,7 +3770,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -3772,8 +3784,8 @@
       <c r="H9" s="10" t="n"/>
       <c r="I9" s="10" t="n"/>
       <c r="J9" s="10" t="n"/>
-      <c r="K9" s="9" t="n"/>
-      <c r="L9" s="9" t="n"/>
+      <c r="K9" s="22" t="n"/>
+      <c r="L9" s="22" t="n"/>
       <c r="M9" s="10" t="n"/>
     </row>
     <row r="10">
@@ -3789,7 +3801,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>KJ</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -3801,9 +3813,9 @@
       <c r="F10" s="10" t="n"/>
       <c r="G10" s="10" t="n"/>
       <c r="H10" s="10" t="n"/>
-      <c r="I10" s="9" t="n"/>
-      <c r="J10" s="9" t="n"/>
-      <c r="K10" s="9" t="n"/>
+      <c r="I10" s="23" t="n"/>
+      <c r="J10" s="23" t="n"/>
+      <c r="K10" s="23" t="n"/>
       <c r="L10" s="10" t="n"/>
       <c r="M10" s="10" t="n"/>
     </row>
@@ -3816,7 +3828,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>KJ</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -3827,10 +3839,10 @@
       <c r="E11" s="10" t="n"/>
       <c r="F11" s="10" t="n"/>
       <c r="G11" s="10" t="n"/>
-      <c r="H11" s="9" t="n"/>
-      <c r="I11" s="9" t="n"/>
-      <c r="J11" s="9" t="n"/>
-      <c r="K11" s="9" t="n"/>
+      <c r="H11" s="23" t="n"/>
+      <c r="I11" s="23" t="n"/>
+      <c r="J11" s="23" t="n"/>
+      <c r="K11" s="23" t="n"/>
       <c r="L11" s="10" t="n"/>
       <c r="M11" s="10" t="n"/>
     </row>
@@ -3843,7 +3855,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>KJ</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -3854,10 +3866,10 @@
       <c r="E12" s="10" t="n"/>
       <c r="F12" s="10" t="n"/>
       <c r="G12" s="10" t="n"/>
-      <c r="H12" s="9" t="n"/>
-      <c r="I12" s="9" t="n"/>
-      <c r="J12" s="9" t="n"/>
-      <c r="K12" s="9" t="n"/>
+      <c r="H12" s="23" t="n"/>
+      <c r="I12" s="23" t="n"/>
+      <c r="J12" s="23" t="n"/>
+      <c r="K12" s="23" t="n"/>
       <c r="L12" s="10" t="n"/>
       <c r="M12" s="10" t="n"/>
     </row>
@@ -3870,7 +3882,7 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>KJ</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -3884,8 +3896,8 @@
       <c r="H13" s="10" t="n"/>
       <c r="I13" s="10" t="n"/>
       <c r="J13" s="10" t="n"/>
-      <c r="K13" s="9" t="n"/>
-      <c r="L13" s="9" t="n"/>
+      <c r="K13" s="23" t="n"/>
+      <c r="L13" s="23" t="n"/>
       <c r="M13" s="10" t="n"/>
     </row>
     <row r="14">
@@ -3901,7 +3913,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>DW, DK</t>
+          <t>DW</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -3955,7 +3967,7 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>DW, DK</t>
+          <t>DW</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -4013,7 +4025,7 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -4024,8 +4036,8 @@
       <c r="E18" s="10" t="n"/>
       <c r="F18" s="10" t="n"/>
       <c r="G18" s="10" t="n"/>
-      <c r="H18" s="9" t="n"/>
-      <c r="I18" s="9" t="n"/>
+      <c r="H18" s="22" t="n"/>
+      <c r="I18" s="22" t="n"/>
       <c r="J18" s="10" t="n"/>
       <c r="K18" s="10" t="n"/>
       <c r="L18" s="10" t="n"/>
@@ -4040,7 +4052,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -4053,8 +4065,8 @@
       <c r="G19" s="10" t="n"/>
       <c r="H19" s="10" t="n"/>
       <c r="I19" s="10" t="n"/>
-      <c r="J19" s="9" t="n"/>
-      <c r="K19" s="9" t="n"/>
+      <c r="J19" s="22" t="n"/>
+      <c r="K19" s="22" t="n"/>
       <c r="L19" s="10" t="n"/>
       <c r="M19" s="10" t="n"/>
     </row>
@@ -4067,7 +4079,7 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -4079,7 +4091,7 @@
       <c r="F20" s="10" t="n"/>
       <c r="G20" s="10" t="n"/>
       <c r="H20" s="10" t="n"/>
-      <c r="I20" s="9" t="n"/>
+      <c r="I20" s="22" t="n"/>
       <c r="J20" s="10" t="n"/>
       <c r="K20" s="10" t="n"/>
       <c r="L20" s="10" t="n"/>
@@ -4098,7 +4110,7 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>MK</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -4109,9 +4121,9 @@
       <c r="E21" s="10" t="n"/>
       <c r="F21" s="10" t="n"/>
       <c r="G21" s="10" t="n"/>
-      <c r="H21" s="9" t="n"/>
-      <c r="I21" s="9" t="n"/>
-      <c r="J21" s="9" t="n"/>
+      <c r="H21" s="11" t="n"/>
+      <c r="I21" s="11" t="n"/>
+      <c r="J21" s="11" t="n"/>
       <c r="K21" s="10" t="n"/>
       <c r="L21" s="10" t="n"/>
       <c r="M21" s="10" t="n"/>
@@ -4129,7 +4141,7 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>MK</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -4141,8 +4153,8 @@
       <c r="F22" s="10" t="n"/>
       <c r="G22" s="10" t="n"/>
       <c r="H22" s="10" t="n"/>
-      <c r="I22" s="9" t="n"/>
-      <c r="J22" s="9" t="n"/>
+      <c r="I22" s="11" t="n"/>
+      <c r="J22" s="11" t="n"/>
       <c r="K22" s="10" t="n"/>
       <c r="L22" s="10" t="n"/>
       <c r="M22" s="10" t="n"/>
@@ -4156,7 +4168,7 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>MK</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -4167,9 +4179,9 @@
       <c r="E23" s="10" t="n"/>
       <c r="F23" s="10" t="n"/>
       <c r="G23" s="10" t="n"/>
-      <c r="H23" s="9" t="n"/>
-      <c r="I23" s="9" t="n"/>
-      <c r="J23" s="9" t="n"/>
+      <c r="H23" s="11" t="n"/>
+      <c r="I23" s="11" t="n"/>
+      <c r="J23" s="11" t="n"/>
       <c r="K23" s="10" t="n"/>
       <c r="L23" s="10" t="n"/>
       <c r="M23" s="10" t="n"/>
@@ -4183,7 +4195,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>MK</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -4197,8 +4209,8 @@
       <c r="H24" s="10" t="n"/>
       <c r="I24" s="10" t="n"/>
       <c r="J24" s="10" t="n"/>
-      <c r="K24" s="9" t="n"/>
-      <c r="L24" s="9" t="n"/>
+      <c r="K24" s="11" t="n"/>
+      <c r="L24" s="11" t="n"/>
       <c r="M24" s="10" t="n"/>
     </row>
     <row r="25">
@@ -4214,7 +4226,7 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>MK, DW</t>
+          <t>KJ</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -4222,10 +4234,10 @@
           <t>6/19~7/10</t>
         </is>
       </c>
-      <c r="E25" s="11" t="n"/>
-      <c r="F25" s="11" t="n"/>
-      <c r="G25" s="11" t="n"/>
-      <c r="H25" s="11" t="n"/>
+      <c r="E25" s="23" t="n"/>
+      <c r="F25" s="23" t="n"/>
+      <c r="G25" s="23" t="n"/>
+      <c r="H25" s="23" t="n"/>
       <c r="I25" s="10" t="n"/>
       <c r="J25" s="10" t="n"/>
       <c r="K25" s="10" t="n"/>
@@ -4241,7 +4253,7 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>KJ</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -4252,9 +4264,9 @@
       <c r="E26" s="10" t="n"/>
       <c r="F26" s="10" t="n"/>
       <c r="G26" s="10" t="n"/>
-      <c r="H26" s="9" t="n"/>
-      <c r="I26" s="9" t="n"/>
-      <c r="J26" s="9" t="n"/>
+      <c r="H26" s="23" t="n"/>
+      <c r="I26" s="23" t="n"/>
+      <c r="J26" s="23" t="n"/>
       <c r="K26" s="10" t="n"/>
       <c r="L26" s="10" t="n"/>
       <c r="M26" s="10" t="n"/>
@@ -4268,7 +4280,7 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>KJ</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -4282,7 +4294,7 @@
       <c r="H27" s="10" t="n"/>
       <c r="I27" s="10" t="n"/>
       <c r="J27" s="10" t="n"/>
-      <c r="K27" s="9" t="n"/>
+      <c r="K27" s="23" t="n"/>
       <c r="L27" s="10" t="n"/>
       <c r="M27" s="10" t="n"/>
     </row>
@@ -4299,7 +4311,7 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>MK</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -4311,8 +4323,8 @@
       <c r="F28" s="10" t="n"/>
       <c r="G28" s="10" t="n"/>
       <c r="H28" s="10" t="n"/>
-      <c r="I28" s="9" t="n"/>
-      <c r="J28" s="9" t="n"/>
+      <c r="I28" s="11" t="n"/>
+      <c r="J28" s="11" t="n"/>
       <c r="K28" s="10" t="n"/>
       <c r="L28" s="10" t="n"/>
       <c r="M28" s="10" t="n"/>
@@ -4326,7 +4338,7 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>MK</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
@@ -4339,8 +4351,8 @@
       <c r="G29" s="10" t="n"/>
       <c r="H29" s="10" t="n"/>
       <c r="I29" s="10" t="n"/>
-      <c r="J29" s="9" t="n"/>
-      <c r="K29" s="9" t="n"/>
+      <c r="J29" s="11" t="n"/>
+      <c r="K29" s="11" t="n"/>
       <c r="L29" s="10" t="n"/>
       <c r="M29" s="10" t="n"/>
     </row>
@@ -4353,7 +4365,7 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>MK</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -4367,8 +4379,8 @@
       <c r="H30" s="10" t="n"/>
       <c r="I30" s="10" t="n"/>
       <c r="J30" s="10" t="n"/>
-      <c r="K30" s="9" t="n"/>
-      <c r="L30" s="9" t="n"/>
+      <c r="K30" s="11" t="n"/>
+      <c r="L30" s="11" t="n"/>
       <c r="M30" s="10" t="n"/>
     </row>
     <row r="31">
@@ -4384,7 +4396,7 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>MK</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -4398,8 +4410,8 @@
       <c r="H31" s="10" t="n"/>
       <c r="I31" s="10" t="n"/>
       <c r="J31" s="10" t="n"/>
-      <c r="K31" s="9" t="n"/>
-      <c r="L31" s="9" t="n"/>
+      <c r="K31" s="11" t="n"/>
+      <c r="L31" s="11" t="n"/>
       <c r="M31" s="10" t="n"/>
     </row>
     <row r="32">
@@ -4411,7 +4423,7 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>MK</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
@@ -4426,7 +4438,7 @@
       <c r="I32" s="10" t="n"/>
       <c r="J32" s="10" t="n"/>
       <c r="K32" s="10" t="n"/>
-      <c r="L32" s="9" t="n"/>
+      <c r="L32" s="11" t="n"/>
       <c r="M32" s="10" t="n"/>
     </row>
     <row r="33">
@@ -4473,7 +4485,7 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>DW, MK, DK</t>
+          <t>DW</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">

--- a/data/워크숍.xlsx
+++ b/data/워크숍.xlsx
@@ -1329,7 +1329,7 @@
     <row r="36" ht="44" customHeight="1">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>※ 이니셜 범례: DW=강도원, MK=민경욱, KJ=김재현, PJ=박진영. 기존 '준비업무'·'간트차트' 탭의 담당 표기(특히 DK)는 본 R&amp;R 기준으로 재정렬 필요. 분야별 마감은 준비업무 탭 일정 기준(변경 가능).</t>
+          <t>※ 이니셜 범례: DW=강도원, MK=민경욱, KJ=김재현, PJ=박진영. 준비업무·간트차트 탭 담당은 본 R&amp;R 기준으로 재정렬 완료. 분야별 마감은 준비업무 탭 일정 기준(변경 가능).</t>
         </is>
       </c>
     </row>
@@ -2688,12 +2688,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -2784,12 +2784,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -2912,12 +2912,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3008,12 +3008,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>DW</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">

--- a/data/워크숍.xlsx
+++ b/data/워크숍.xlsx
@@ -215,7 +215,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -266,6 +266,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1441,14 +1444,14 @@
           <t>DW</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>6/16</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>7/3</t>
+      <c r="F2" s="24" t="inlineStr">
+        <is>
+          <t>7/1</t>
+        </is>
+      </c>
+      <c r="G2" s="24" t="inlineStr">
+        <is>
+          <t>7/8</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
@@ -1478,12 +1481,12 @@
           <t>DW</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>7/3</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="F3" s="24" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="G3" s="24" t="inlineStr">
         <is>
           <t>7/17</t>
         </is>
@@ -1515,14 +1518,14 @@
           <t>DW</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7/1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7/10</t>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>7/3</t>
+        </is>
+      </c>
+      <c r="G4" s="24" t="inlineStr">
+        <is>
+          <t>7/11</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
@@ -1552,14 +1555,14 @@
           <t>PJ</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>6/22</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>7/3</t>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>7/1</t>
+        </is>
+      </c>
+      <c r="G5" s="24" t="inlineStr">
+        <is>
+          <t>7/8</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -1593,12 +1596,12 @@
           <t>PJ</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="24" t="inlineStr">
         <is>
           <t>8/3</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t>8/4</t>
         </is>
@@ -1634,12 +1637,12 @@
           <t>PJ</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="24" t="inlineStr">
         <is>
           <t>7/22</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="24" t="inlineStr">
         <is>
           <t>7/29</t>
         </is>
@@ -1671,12 +1674,12 @@
           <t>PJ</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7/29</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>8/3</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
         <is>
           <t>8/4</t>
         </is>
@@ -1708,14 +1711,14 @@
           <t>KJ</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>7/17</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>7/29</t>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>7/20</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>7/31</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
@@ -1741,14 +1744,14 @@
           <t>KJ</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7/10</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7/29</t>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>7/31</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -1778,14 +1781,14 @@
           <t>KJ</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>7/8</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>7/29</t>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>7/10</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>7/31</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -1815,12 +1818,12 @@
           <t>KJ</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7/30</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>8/1</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
         <is>
           <t>8/4</t>
         </is>
@@ -1852,14 +1855,14 @@
           <t>DW</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="24" t="inlineStr">
         <is>
           <t>7/3</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7/10</t>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>7/9</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr"/>
@@ -1889,12 +1892,12 @@
           <t>DW</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7/11</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>7/9</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
         <is>
           <t>7/15</t>
         </is>
@@ -1930,12 +1933,12 @@
           <t>DW</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="24" t="inlineStr">
         <is>
           <t>7/15</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="24" t="inlineStr">
         <is>
           <t>7/22</t>
         </is>
@@ -1967,12 +1970,12 @@
           <t>DW</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="24" t="inlineStr">
         <is>
           <t>7/22</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="24" t="inlineStr">
         <is>
           <t>7/29</t>
         </is>
@@ -2000,12 +2003,12 @@
           <t>PJ</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="24" t="inlineStr">
         <is>
           <t>7/9</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="24" t="inlineStr">
         <is>
           <t>7/15</t>
         </is>
@@ -2037,12 +2040,12 @@
           <t>PJ</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="24" t="inlineStr">
         <is>
           <t>7/22</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="24" t="inlineStr">
         <is>
           <t>7/29</t>
         </is>
@@ -2074,14 +2077,14 @@
           <t>PJ</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>7/13</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>7/17</t>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>7/18</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
@@ -2107,12 +2110,12 @@
           <t>MK</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>7/10</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>7/17</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
         <is>
           <t>7/24</t>
         </is>
@@ -2148,14 +2151,14 @@
           <t>MK</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>7/13</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>7/22</t>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>7/18</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -2189,14 +2192,14 @@
           <t>MK</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" s="24" t="inlineStr">
         <is>
           <t>7/8</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>7/22</t>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>7/18</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -2234,12 +2237,12 @@
           <t>MK</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" s="24" t="inlineStr">
         <is>
           <t>8/1</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="24" t="inlineStr">
         <is>
           <t>8/4</t>
         </is>
@@ -2271,14 +2274,14 @@
           <t>KJ</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>6/19</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>7/10</t>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>7/1</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>7/8</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
@@ -2308,12 +2311,12 @@
           <t>KJ</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>7/11</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>7/8</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
         <is>
           <t>7/24</t>
         </is>
@@ -2345,12 +2348,12 @@
           <t>KJ</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>7/28</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>7/24</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
         <is>
           <t>7/31</t>
         </is>
@@ -2382,12 +2385,12 @@
           <t>MK</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" s="24" t="inlineStr">
         <is>
           <t>7/18</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="24" t="inlineStr">
         <is>
           <t>7/24</t>
         </is>
@@ -2423,12 +2426,12 @@
           <t>MK</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" s="24" t="inlineStr">
         <is>
           <t>7/25</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="24" t="inlineStr">
         <is>
           <t>7/31</t>
         </is>
@@ -2460,12 +2463,12 @@
           <t>MK</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" s="24" t="inlineStr">
         <is>
           <t>7/31</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" s="24" t="inlineStr">
         <is>
           <t>8/4</t>
         </is>
@@ -2493,12 +2496,12 @@
           <t>MK</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>8/1</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="inlineStr">
         <is>
           <t>8/4</t>
         </is>
@@ -2530,12 +2533,12 @@
           <t>MK</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" s="24" t="inlineStr">
         <is>
           <t>8/5</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" s="24" t="inlineStr">
         <is>
           <t>8/5</t>
         </is>
@@ -2567,12 +2570,12 @@
           <t>DW</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F32" s="24" t="inlineStr">
         <is>
           <t>8/6</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" s="24" t="inlineStr">
         <is>
           <t>8/14</t>
         </is>
@@ -2604,12 +2607,12 @@
           <t>DW</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" s="24" t="inlineStr">
         <is>
           <t>8/4</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" s="24" t="inlineStr">
         <is>
           <t>8/4</t>
         </is>
@@ -3499,7 +3502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3513,8 +3516,6 @@
     <col width="5" customWidth="1" min="9" max="9"/>
     <col width="5" customWidth="1" min="10" max="10"/>
     <col width="5" customWidth="1" min="11" max="11"/>
-    <col width="5" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3547,45 +3548,35 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>6/29</t>
         </is>
       </c>
       <c r="F2" s="6" t="inlineStr">
         <is>
-          <t>6/22</t>
+          <t>7/6</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/13</t>
         </is>
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>7/6</t>
+          <t>7/20</t>
         </is>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>7/27</t>
         </is>
       </c>
       <c r="J2" s="6" t="inlineStr">
         <is>
-          <t>7/20</t>
+          <t>8/3</t>
         </is>
       </c>
       <c r="K2" s="6" t="inlineStr">
-        <is>
-          <t>7/27</t>
-        </is>
-      </c>
-      <c r="L2" s="6" t="inlineStr">
-        <is>
-          <t>8/3</t>
-        </is>
-      </c>
-      <c r="M2" s="6" t="inlineStr">
         <is>
           <t>8/10</t>
         </is>
@@ -3609,18 +3600,16 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>6/16~7/3</t>
+          <t>7/1~7/8</t>
         </is>
       </c>
       <c r="E3" s="9" t="n"/>
       <c r="F3" s="9" t="n"/>
-      <c r="G3" s="9" t="n"/>
+      <c r="G3" s="10" t="n"/>
       <c r="H3" s="10" t="n"/>
       <c r="I3" s="10" t="n"/>
       <c r="J3" s="10" t="n"/>
       <c r="K3" s="10" t="n"/>
-      <c r="L3" s="10" t="n"/>
-      <c r="M3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr"/>
@@ -3636,18 +3625,16 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>7/3~7/17</t>
+          <t>7/8~7/17</t>
         </is>
       </c>
       <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
+      <c r="F4" s="9" t="n"/>
       <c r="G4" s="9" t="n"/>
-      <c r="H4" s="9" t="n"/>
-      <c r="I4" s="9" t="n"/>
+      <c r="H4" s="10" t="n"/>
+      <c r="I4" s="10" t="n"/>
       <c r="J4" s="10" t="n"/>
       <c r="K4" s="10" t="n"/>
-      <c r="L4" s="10" t="n"/>
-      <c r="M4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr"/>
@@ -3663,18 +3650,16 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>7/1~7/10</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="n"/>
-      <c r="F5" s="10" t="n"/>
-      <c r="G5" s="9" t="n"/>
-      <c r="H5" s="9" t="n"/>
+          <t>7/3~7/11</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n"/>
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n"/>
       <c r="I5" s="10" t="n"/>
       <c r="J5" s="10" t="n"/>
       <c r="K5" s="10" t="n"/>
-      <c r="L5" s="10" t="n"/>
-      <c r="M5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -3694,18 +3679,16 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>6/22~7/3</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="n"/>
+          <t>7/1~7/8</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="n"/>
       <c r="F6" s="22" t="n"/>
-      <c r="G6" s="22" t="n"/>
+      <c r="G6" s="10" t="n"/>
       <c r="H6" s="10" t="n"/>
       <c r="I6" s="10" t="n"/>
       <c r="J6" s="10" t="n"/>
       <c r="K6" s="10" t="n"/>
-      <c r="L6" s="10" t="n"/>
-      <c r="M6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr"/>
@@ -3729,10 +3712,8 @@
       <c r="G7" s="10" t="n"/>
       <c r="H7" s="10" t="n"/>
       <c r="I7" s="10" t="n"/>
-      <c r="J7" s="10" t="n"/>
+      <c r="J7" s="22" t="n"/>
       <c r="K7" s="10" t="n"/>
-      <c r="L7" s="22" t="n"/>
-      <c r="M7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr"/>
@@ -3754,12 +3735,10 @@
       <c r="E8" s="10" t="n"/>
       <c r="F8" s="10" t="n"/>
       <c r="G8" s="10" t="n"/>
-      <c r="H8" s="10" t="n"/>
-      <c r="I8" s="10" t="n"/>
-      <c r="J8" s="22" t="n"/>
-      <c r="K8" s="22" t="n"/>
-      <c r="L8" s="10" t="n"/>
-      <c r="M8" s="10" t="n"/>
+      <c r="H8" s="22" t="n"/>
+      <c r="I8" s="22" t="n"/>
+      <c r="J8" s="10" t="n"/>
+      <c r="K8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr"/>
@@ -3775,7 +3754,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>7/29~8/4</t>
+          <t>8/3~8/4</t>
         </is>
       </c>
       <c r="E9" s="10" t="n"/>
@@ -3783,10 +3762,8 @@
       <c r="G9" s="10" t="n"/>
       <c r="H9" s="10" t="n"/>
       <c r="I9" s="10" t="n"/>
-      <c r="J9" s="10" t="n"/>
-      <c r="K9" s="22" t="n"/>
-      <c r="L9" s="22" t="n"/>
-      <c r="M9" s="10" t="n"/>
+      <c r="J9" s="22" t="n"/>
+      <c r="K9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -3806,18 +3783,16 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>7/17~7/29</t>
+          <t>7/20~7/31</t>
         </is>
       </c>
       <c r="E10" s="10" t="n"/>
       <c r="F10" s="10" t="n"/>
       <c r="G10" s="10" t="n"/>
-      <c r="H10" s="10" t="n"/>
+      <c r="H10" s="23" t="n"/>
       <c r="I10" s="23" t="n"/>
-      <c r="J10" s="23" t="n"/>
-      <c r="K10" s="23" t="n"/>
-      <c r="L10" s="10" t="n"/>
-      <c r="M10" s="10" t="n"/>
+      <c r="J10" s="10" t="n"/>
+      <c r="K10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr"/>
@@ -3833,18 +3808,16 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>7/10~7/29</t>
+          <t>7/14~7/31</t>
         </is>
       </c>
       <c r="E11" s="10" t="n"/>
       <c r="F11" s="10" t="n"/>
-      <c r="G11" s="10" t="n"/>
+      <c r="G11" s="23" t="n"/>
       <c r="H11" s="23" t="n"/>
       <c r="I11" s="23" t="n"/>
-      <c r="J11" s="23" t="n"/>
-      <c r="K11" s="23" t="n"/>
-      <c r="L11" s="10" t="n"/>
-      <c r="M11" s="10" t="n"/>
+      <c r="J11" s="10" t="n"/>
+      <c r="K11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr"/>
@@ -3860,18 +3833,16 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>7/8~7/29</t>
+          <t>7/10~7/31</t>
         </is>
       </c>
       <c r="E12" s="10" t="n"/>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
+      <c r="F12" s="23" t="n"/>
+      <c r="G12" s="23" t="n"/>
       <c r="H12" s="23" t="n"/>
       <c r="I12" s="23" t="n"/>
-      <c r="J12" s="23" t="n"/>
-      <c r="K12" s="23" t="n"/>
-      <c r="L12" s="10" t="n"/>
-      <c r="M12" s="10" t="n"/>
+      <c r="J12" s="10" t="n"/>
+      <c r="K12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr"/>
@@ -3887,18 +3858,16 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>7/30~8/4</t>
+          <t>8/1~8/4</t>
         </is>
       </c>
       <c r="E13" s="10" t="n"/>
       <c r="F13" s="10" t="n"/>
       <c r="G13" s="10" t="n"/>
       <c r="H13" s="10" t="n"/>
-      <c r="I13" s="10" t="n"/>
-      <c r="J13" s="10" t="n"/>
-      <c r="K13" s="23" t="n"/>
-      <c r="L13" s="23" t="n"/>
-      <c r="M13" s="10" t="n"/>
+      <c r="I13" s="23" t="n"/>
+      <c r="J13" s="23" t="n"/>
+      <c r="K13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -3918,18 +3887,16 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>7/3~7/10</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="9" t="n"/>
-      <c r="H14" s="9" t="n"/>
+          <t>7/3~7/9</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="10" t="n"/>
       <c r="I14" s="10" t="n"/>
       <c r="J14" s="10" t="n"/>
       <c r="K14" s="10" t="n"/>
-      <c r="L14" s="10" t="n"/>
-      <c r="M14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr"/>
@@ -3945,18 +3912,16 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>7/11~7/15</t>
+          <t>7/9~7/15</t>
         </is>
       </c>
       <c r="E15" s="10" t="n"/>
-      <c r="F15" s="10" t="n"/>
-      <c r="G15" s="10" t="n"/>
-      <c r="H15" s="9" t="n"/>
-      <c r="I15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="10" t="n"/>
+      <c r="I15" s="10" t="n"/>
       <c r="J15" s="10" t="n"/>
       <c r="K15" s="10" t="n"/>
-      <c r="L15" s="10" t="n"/>
-      <c r="M15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr"/>
@@ -3977,13 +3942,11 @@
       </c>
       <c r="E16" s="10" t="n"/>
       <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
-      <c r="H16" s="10" t="n"/>
-      <c r="I16" s="9" t="n"/>
-      <c r="J16" s="9" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="9" t="n"/>
+      <c r="I16" s="10" t="n"/>
+      <c r="J16" s="10" t="n"/>
       <c r="K16" s="10" t="n"/>
-      <c r="L16" s="10" t="n"/>
-      <c r="M16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr"/>
@@ -4005,12 +3968,10 @@
       <c r="E17" s="10" t="n"/>
       <c r="F17" s="10" t="n"/>
       <c r="G17" s="10" t="n"/>
-      <c r="H17" s="10" t="n"/>
-      <c r="I17" s="10" t="n"/>
-      <c r="J17" s="9" t="n"/>
-      <c r="K17" s="9" t="n"/>
-      <c r="L17" s="10" t="n"/>
-      <c r="M17" s="10" t="n"/>
+      <c r="H17" s="9" t="n"/>
+      <c r="I17" s="9" t="n"/>
+      <c r="J17" s="10" t="n"/>
+      <c r="K17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -4034,14 +3995,12 @@
         </is>
       </c>
       <c r="E18" s="10" t="n"/>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10" t="n"/>
-      <c r="H18" s="22" t="n"/>
-      <c r="I18" s="22" t="n"/>
+      <c r="F18" s="22" t="n"/>
+      <c r="G18" s="22" t="n"/>
+      <c r="H18" s="10" t="n"/>
+      <c r="I18" s="10" t="n"/>
       <c r="J18" s="10" t="n"/>
       <c r="K18" s="10" t="n"/>
-      <c r="L18" s="10" t="n"/>
-      <c r="M18" s="10" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr"/>
@@ -4063,12 +4022,10 @@
       <c r="E19" s="10" t="n"/>
       <c r="F19" s="10" t="n"/>
       <c r="G19" s="10" t="n"/>
-      <c r="H19" s="10" t="n"/>
-      <c r="I19" s="10" t="n"/>
-      <c r="J19" s="22" t="n"/>
-      <c r="K19" s="22" t="n"/>
-      <c r="L19" s="10" t="n"/>
-      <c r="M19" s="10" t="n"/>
+      <c r="H19" s="22" t="n"/>
+      <c r="I19" s="22" t="n"/>
+      <c r="J19" s="10" t="n"/>
+      <c r="K19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr"/>
@@ -4084,18 +4041,16 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>7/13~7/17</t>
+          <t>7/14~7/18</t>
         </is>
       </c>
       <c r="E20" s="10" t="n"/>
       <c r="F20" s="10" t="n"/>
-      <c r="G20" s="10" t="n"/>
+      <c r="G20" s="22" t="n"/>
       <c r="H20" s="10" t="n"/>
-      <c r="I20" s="22" t="n"/>
+      <c r="I20" s="10" t="n"/>
       <c r="J20" s="10" t="n"/>
       <c r="K20" s="10" t="n"/>
-      <c r="L20" s="10" t="n"/>
-      <c r="M20" s="10" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -4115,18 +4070,16 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>7/10~7/24</t>
+          <t>7/17~7/24</t>
         </is>
       </c>
       <c r="E21" s="10" t="n"/>
       <c r="F21" s="10" t="n"/>
-      <c r="G21" s="10" t="n"/>
+      <c r="G21" s="11" t="n"/>
       <c r="H21" s="11" t="n"/>
-      <c r="I21" s="11" t="n"/>
-      <c r="J21" s="11" t="n"/>
+      <c r="I21" s="10" t="n"/>
+      <c r="J21" s="10" t="n"/>
       <c r="K21" s="10" t="n"/>
-      <c r="L21" s="10" t="n"/>
-      <c r="M21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -4146,18 +4099,16 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>7/13~7/22</t>
+          <t>7/8~7/18</t>
         </is>
       </c>
       <c r="E22" s="10" t="n"/>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="10" t="n"/>
+      <c r="F22" s="11" t="n"/>
+      <c r="G22" s="11" t="n"/>
       <c r="H22" s="10" t="n"/>
-      <c r="I22" s="11" t="n"/>
-      <c r="J22" s="11" t="n"/>
+      <c r="I22" s="10" t="n"/>
+      <c r="J22" s="10" t="n"/>
       <c r="K22" s="10" t="n"/>
-      <c r="L22" s="10" t="n"/>
-      <c r="M22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr"/>
@@ -4173,18 +4124,16 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>7/8~7/22</t>
+          <t>7/8~7/18</t>
         </is>
       </c>
       <c r="E23" s="10" t="n"/>
-      <c r="F23" s="10" t="n"/>
-      <c r="G23" s="10" t="n"/>
-      <c r="H23" s="11" t="n"/>
-      <c r="I23" s="11" t="n"/>
-      <c r="J23" s="11" t="n"/>
+      <c r="F23" s="11" t="n"/>
+      <c r="G23" s="11" t="n"/>
+      <c r="H23" s="10" t="n"/>
+      <c r="I23" s="10" t="n"/>
+      <c r="J23" s="10" t="n"/>
       <c r="K23" s="10" t="n"/>
-      <c r="L23" s="10" t="n"/>
-      <c r="M23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr"/>
@@ -4207,11 +4156,9 @@
       <c r="F24" s="10" t="n"/>
       <c r="G24" s="10" t="n"/>
       <c r="H24" s="10" t="n"/>
-      <c r="I24" s="10" t="n"/>
-      <c r="J24" s="10" t="n"/>
-      <c r="K24" s="11" t="n"/>
-      <c r="L24" s="11" t="n"/>
-      <c r="M24" s="10" t="n"/>
+      <c r="I24" s="11" t="n"/>
+      <c r="J24" s="11" t="n"/>
+      <c r="K24" s="10" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -4231,18 +4178,16 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>6/19~7/10</t>
+          <t>7/1~7/8</t>
         </is>
       </c>
       <c r="E25" s="23" t="n"/>
       <c r="F25" s="23" t="n"/>
-      <c r="G25" s="23" t="n"/>
-      <c r="H25" s="23" t="n"/>
+      <c r="G25" s="10" t="n"/>
+      <c r="H25" s="10" t="n"/>
       <c r="I25" s="10" t="n"/>
       <c r="J25" s="10" t="n"/>
       <c r="K25" s="10" t="n"/>
-      <c r="L25" s="10" t="n"/>
-      <c r="M25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr"/>
@@ -4258,18 +4203,16 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>7/11~7/24</t>
+          <t>7/8~7/24</t>
         </is>
       </c>
       <c r="E26" s="10" t="n"/>
-      <c r="F26" s="10" t="n"/>
-      <c r="G26" s="10" t="n"/>
+      <c r="F26" s="23" t="n"/>
+      <c r="G26" s="23" t="n"/>
       <c r="H26" s="23" t="n"/>
-      <c r="I26" s="23" t="n"/>
-      <c r="J26" s="23" t="n"/>
+      <c r="I26" s="10" t="n"/>
+      <c r="J26" s="10" t="n"/>
       <c r="K26" s="10" t="n"/>
-      <c r="L26" s="10" t="n"/>
-      <c r="M26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr"/>
@@ -4285,18 +4228,16 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>7/28~7/31</t>
+          <t>7/24~7/31</t>
         </is>
       </c>
       <c r="E27" s="10" t="n"/>
       <c r="F27" s="10" t="n"/>
       <c r="G27" s="10" t="n"/>
-      <c r="H27" s="10" t="n"/>
-      <c r="I27" s="10" t="n"/>
+      <c r="H27" s="23" t="n"/>
+      <c r="I27" s="23" t="n"/>
       <c r="J27" s="10" t="n"/>
-      <c r="K27" s="23" t="n"/>
-      <c r="L27" s="10" t="n"/>
-      <c r="M27" s="10" t="n"/>
+      <c r="K27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -4321,13 +4262,11 @@
       </c>
       <c r="E28" s="10" t="n"/>
       <c r="F28" s="10" t="n"/>
-      <c r="G28" s="10" t="n"/>
-      <c r="H28" s="10" t="n"/>
-      <c r="I28" s="11" t="n"/>
-      <c r="J28" s="11" t="n"/>
+      <c r="G28" s="11" t="n"/>
+      <c r="H28" s="11" t="n"/>
+      <c r="I28" s="10" t="n"/>
+      <c r="J28" s="10" t="n"/>
       <c r="K28" s="10" t="n"/>
-      <c r="L28" s="10" t="n"/>
-      <c r="M28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr"/>
@@ -4349,12 +4288,10 @@
       <c r="E29" s="10" t="n"/>
       <c r="F29" s="10" t="n"/>
       <c r="G29" s="10" t="n"/>
-      <c r="H29" s="10" t="n"/>
-      <c r="I29" s="10" t="n"/>
-      <c r="J29" s="11" t="n"/>
-      <c r="K29" s="11" t="n"/>
-      <c r="L29" s="10" t="n"/>
-      <c r="M29" s="10" t="n"/>
+      <c r="H29" s="11" t="n"/>
+      <c r="I29" s="11" t="n"/>
+      <c r="J29" s="10" t="n"/>
+      <c r="K29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr"/>
@@ -4377,11 +4314,9 @@
       <c r="F30" s="10" t="n"/>
       <c r="G30" s="10" t="n"/>
       <c r="H30" s="10" t="n"/>
-      <c r="I30" s="10" t="n"/>
-      <c r="J30" s="10" t="n"/>
-      <c r="K30" s="11" t="n"/>
-      <c r="L30" s="11" t="n"/>
-      <c r="M30" s="10" t="n"/>
+      <c r="I30" s="11" t="n"/>
+      <c r="J30" s="11" t="n"/>
+      <c r="K30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -4401,18 +4336,16 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>8/1~8/4</t>
+          <t>7/28~8/4</t>
         </is>
       </c>
       <c r="E31" s="10" t="n"/>
       <c r="F31" s="10" t="n"/>
       <c r="G31" s="10" t="n"/>
       <c r="H31" s="10" t="n"/>
-      <c r="I31" s="10" t="n"/>
-      <c r="J31" s="10" t="n"/>
-      <c r="K31" s="11" t="n"/>
-      <c r="L31" s="11" t="n"/>
-      <c r="M31" s="10" t="n"/>
+      <c r="I31" s="11" t="n"/>
+      <c r="J31" s="11" t="n"/>
+      <c r="K31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr"/>
@@ -4436,10 +4369,8 @@
       <c r="G32" s="10" t="n"/>
       <c r="H32" s="10" t="n"/>
       <c r="I32" s="10" t="n"/>
-      <c r="J32" s="10" t="n"/>
+      <c r="J32" s="11" t="n"/>
       <c r="K32" s="10" t="n"/>
-      <c r="L32" s="11" t="n"/>
-      <c r="M32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -4467,10 +4398,8 @@
       <c r="G33" s="10" t="n"/>
       <c r="H33" s="10" t="n"/>
       <c r="I33" s="10" t="n"/>
-      <c r="J33" s="10" t="n"/>
-      <c r="K33" s="10" t="n"/>
-      <c r="L33" s="9" t="n"/>
-      <c r="M33" s="9" t="n"/>
+      <c r="J33" s="9" t="n"/>
+      <c r="K33" s="9" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -4498,14 +4427,12 @@
       <c r="G34" s="10" t="n"/>
       <c r="H34" s="10" t="n"/>
       <c r="I34" s="10" t="n"/>
-      <c r="J34" s="10" t="n"/>
+      <c r="J34" s="9" t="n"/>
       <c r="K34" s="10" t="n"/>
-      <c r="L34" s="9" t="n"/>
-      <c r="M34" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/워크숍.xlsx
+++ b/data/워크숍.xlsx
@@ -726,7 +726,7 @@
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>KU</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
@@ -753,7 +753,7 @@
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>KJ</t>
+          <t>JH</t>
         </is>
       </c>
       <c r="B8" s="17" t="inlineStr">
@@ -780,7 +780,7 @@
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>김재현(KJ)</t>
+          <t>김재현(JH)</t>
         </is>
       </c>
       <c r="C17" s="18" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>김재현(KJ)</t>
+          <t>김재현(JH)</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>민경욱(MK)</t>
+          <t>민경욱(KU)</t>
         </is>
       </c>
       <c r="C19" s="18" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>민경욱(MK)</t>
+          <t>민경욱(KU)</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>민경욱(MK)</t>
+          <t>민경욱(KU)</t>
         </is>
       </c>
       <c r="C21" s="18" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>민경욱(MK)</t>
+          <t>민경욱(KU)</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>박진영(PJ)</t>
+          <t>박진영(JY)</t>
         </is>
       </c>
       <c r="C23" s="18" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>박진영(PJ)</t>
+          <t>박진영(JY)</t>
         </is>
       </c>
       <c r="C24" s="18" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>김재현(KJ)</t>
+          <t>김재현(JH)</t>
         </is>
       </c>
       <c r="C29" s="18" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>박진영(PJ)</t>
+          <t>박진영(JY)</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>민경욱(MK)</t>
+          <t>민경욱(KU)</t>
         </is>
       </c>
       <c r="C31" s="18" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>김재현(KJ)</t>
+          <t>김재현(JH)</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>민경욱(MK)</t>
+          <t>민경욱(KU)</t>
         </is>
       </c>
       <c r="C33" s="18" t="inlineStr">
@@ -1332,7 +1332,7 @@
     <row r="36" ht="44" customHeight="1">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>※ 이니셜 범례: DW=강도원, MK=민경욱, KJ=김재현, PJ=박진영. 준비업무·간트차트 탭 담당은 본 R&amp;R 기준으로 재정렬 완료. 분야별 마감은 준비업무 탭 일정 기준(변경 가능).</t>
+          <t>※ 이니셜 범례: DW=강도원, KU=민경욱, JH=김재현, JY=박진영. 준비업무·간트차트 탭 담당은 본 R&amp;R 기준으로 재정렬 완료. 분야별 마감은 준비업무 탭 일정 기준(변경 가능).</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="F5" s="24" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="F7" s="24" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="F8" s="24" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>KJ</t>
+          <t>JH</t>
         </is>
       </c>
       <c r="F9" s="24" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>KJ</t>
+          <t>JH</t>
         </is>
       </c>
       <c r="F10" s="24" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>KJ</t>
+          <t>JH</t>
         </is>
       </c>
       <c r="F11" s="24" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>KJ</t>
+          <t>JH</t>
         </is>
       </c>
       <c r="F12" s="24" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="F17" s="24" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="F18" s="24" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="F19" s="24" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>KU</t>
         </is>
       </c>
       <c r="F20" s="24" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>KU</t>
         </is>
       </c>
       <c r="F21" s="24" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>KU</t>
         </is>
       </c>
       <c r="F22" s="24" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>KU</t>
         </is>
       </c>
       <c r="F23" s="24" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>KJ</t>
+          <t>JH</t>
         </is>
       </c>
       <c r="F24" s="24" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>KJ</t>
+          <t>JH</t>
         </is>
       </c>
       <c r="F25" s="24" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>KJ</t>
+          <t>JH</t>
         </is>
       </c>
       <c r="F26" s="24" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>KU</t>
         </is>
       </c>
       <c r="F27" s="24" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>KU</t>
         </is>
       </c>
       <c r="F28" s="24" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>KU</t>
         </is>
       </c>
       <c r="F29" s="24" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>KU</t>
         </is>
       </c>
       <c r="F30" s="24" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>KU</t>
         </is>
       </c>
       <c r="F31" s="24" t="inlineStr">
@@ -2691,12 +2691,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -2723,12 +2723,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -2819,12 +2819,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -2883,12 +2883,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2947,12 +2947,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3011,12 +3011,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>KJ</t>
+          <t>JH</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>KJ</t>
+          <t>JH</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>KJ</t>
+          <t>JH</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>KJ</t>
+          <t>JH</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JY</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>KU</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>KU</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>KU</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>KU</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>KJ</t>
+          <t>JH</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>KJ</t>
+          <t>JH</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>KJ</t>
+          <t>JH</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>KU</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>KU</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>KU</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>KU</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>MK</t>
+          <t>KU</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">

--- a/data/워크숍.xlsx
+++ b/data/워크숍.xlsx
@@ -1363,7 +1363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>대전 숙소 안내 (필요 시)</t>
+          <t>방문자 출입 등록·주차 안내 (연구원 보안 절차)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2387,19 +2387,15 @@
       </c>
       <c r="F27" s="24" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>7/25</t>
         </is>
       </c>
       <c r="G27" s="24" t="inlineStr">
         <is>
-          <t>7/24</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>DLR 도착 일정 확인</t>
-        </is>
-      </c>
+          <t>7/31</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
@@ -2418,7 +2414,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>방문자 출입 등록·주차 안내 (연구원 보안 절차)</t>
+          <t>원내 안내 표지판·동선 표시</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2428,12 +2424,12 @@
       </c>
       <c r="F28" s="24" t="inlineStr">
         <is>
-          <t>7/25</t>
+          <t>7/31</t>
         </is>
       </c>
       <c r="G28" s="24" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>8/4</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -2441,21 +2437,17 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>의전·영접</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>DLR 손님</t>
-        </is>
-      </c>
+          <t>사진·기록</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr"/>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>원내 안내 표지판·동선 표시</t>
+          <t>기념 촬영 담당 지정 및 구도·단체사진 위치 사전 확인</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2465,7 +2457,7 @@
       </c>
       <c r="F29" s="24" t="inlineStr">
         <is>
-          <t>7/31</t>
+          <t>7/28</t>
         </is>
       </c>
       <c r="G29" s="24" t="inlineStr">
@@ -2473,7 +2465,11 @@
           <t>8/4</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr"/>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>11:50~12:00 촬영</t>
+        </is>
+      </c>
       <c r="I29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
@@ -2488,7 +2484,7 @@
       <c r="C30" s="3" t="inlineStr"/>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>기념 촬영 담당 지정 및 구도·단체사진 위치 사전 확인</t>
+          <t>행사 진행 사진·기록 정리</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2498,71 +2494,71 @@
       </c>
       <c r="F30" s="24" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/5</t>
         </is>
       </c>
       <c r="G30" s="24" t="inlineStr">
         <is>
-          <t>8/4</t>
+          <t>8/5</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>11:50~12:00 촬영</t>
+          <t>행사 당일</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>사진·기록</t>
+          <t>비용 처리</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr"/>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>행사 진행 사진·기록 정리</t>
+          <t>인쇄비·기념품·다과·중식·회의비 등 정산 및 결재</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>KU</t>
+          <t>DW</t>
         </is>
       </c>
       <c r="F31" s="24" t="inlineStr">
         <is>
-          <t>8/5</t>
+          <t>8/6</t>
         </is>
       </c>
       <c r="G31" s="24" t="inlineStr">
         <is>
-          <t>8/5</t>
+          <t>8/14</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>행사 당일</t>
+          <t>총괄과제 인쇄비 등</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>비용 처리</t>
+          <t>최종 점검</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr"/>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>인쇄비·기념품·다과·중식·회의비 등 정산 및 결재</t>
+          <t>전일 전체 세팅·리허설 점검 (회의실·자료·물품·동선 일괄 확인)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2572,57 +2568,20 @@
       </c>
       <c r="F32" s="24" t="inlineStr">
         <is>
-          <t>8/6</t>
+          <t>8/4</t>
         </is>
       </c>
       <c r="G32" s="24" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>8/4</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>총괄과제 인쇄비 등</t>
+          <t>체크리스트 일괄 검토</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>최종 점검</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>전일 전체 세팅·리허설 점검 (회의실·자료·물품·동선 일괄 확인)</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>DW</t>
-        </is>
-      </c>
-      <c r="F33" s="24" t="inlineStr">
-        <is>
-          <t>8/4</t>
-        </is>
-      </c>
-      <c r="G33" s="24" t="inlineStr">
-        <is>
-          <t>8/4</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>체크리스트 일괄 검토</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3502,7 +3461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4247,7 +4206,7 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>대전 숙소 안내 (필요 시)</t>
+          <t>방문자 출입 등록·주차 안내 (연구원 보안 절차)</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -4257,14 +4216,14 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>7/18~7/24</t>
+          <t>7/25~7/31</t>
         </is>
       </c>
       <c r="E28" s="10" t="n"/>
       <c r="F28" s="10" t="n"/>
-      <c r="G28" s="11" t="n"/>
+      <c r="G28" s="10" t="n"/>
       <c r="H28" s="11" t="n"/>
-      <c r="I28" s="10" t="n"/>
+      <c r="I28" s="11" t="n"/>
       <c r="J28" s="10" t="n"/>
       <c r="K28" s="10" t="n"/>
     </row>
@@ -4272,7 +4231,7 @@
       <c r="A29" s="7" t="inlineStr"/>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>방문자 출입 등록·주차 안내 (연구원 보안 절차)</t>
+          <t>원내 안내 표지판·동선 표시</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
@@ -4282,22 +4241,26 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>7/25~7/31</t>
+          <t>7/31~8/4</t>
         </is>
       </c>
       <c r="E29" s="10" t="n"/>
       <c r="F29" s="10" t="n"/>
       <c r="G29" s="10" t="n"/>
-      <c r="H29" s="11" t="n"/>
+      <c r="H29" s="10" t="n"/>
       <c r="I29" s="11" t="n"/>
-      <c r="J29" s="10" t="n"/>
+      <c r="J29" s="11" t="n"/>
       <c r="K29" s="10" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr"/>
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>사진·기록</t>
+        </is>
+      </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>원내 안내 표지판·동선 표시</t>
+          <t>기념 촬영 담당 지정 및 구도·단체사진 위치 사전 확인</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
@@ -4307,7 +4270,7 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>7/31~8/4</t>
+          <t>7/28~8/4</t>
         </is>
       </c>
       <c r="E30" s="10" t="n"/>
@@ -4319,14 +4282,10 @@
       <c r="K30" s="10" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>사진·기록</t>
-        </is>
-      </c>
+      <c r="A31" s="7" t="inlineStr"/>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>기념 촬영 담당 지정 및 구도·단체사진 위치 사전 확인</t>
+          <t>행사 진행 사진·기록 정리</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -4336,32 +4295,36 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>7/28~8/4</t>
+          <t>8/5~8/5</t>
         </is>
       </c>
       <c r="E31" s="10" t="n"/>
       <c r="F31" s="10" t="n"/>
       <c r="G31" s="10" t="n"/>
       <c r="H31" s="10" t="n"/>
-      <c r="I31" s="11" t="n"/>
+      <c r="I31" s="10" t="n"/>
       <c r="J31" s="11" t="n"/>
       <c r="K31" s="10" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr"/>
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>비용 처리</t>
+        </is>
+      </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>행사 진행 사진·기록 정리</t>
+          <t>인쇄비·기념품·다과·중식·회의비 등 정산 및 결재</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>KU</t>
+          <t>DW</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>8/5~8/5</t>
+          <t>8/6~8/14</t>
         </is>
       </c>
       <c r="E32" s="10" t="n"/>
@@ -4369,18 +4332,18 @@
       <c r="G32" s="10" t="n"/>
       <c r="H32" s="10" t="n"/>
       <c r="I32" s="10" t="n"/>
-      <c r="J32" s="11" t="n"/>
-      <c r="K32" s="10" t="n"/>
+      <c r="J32" s="9" t="n"/>
+      <c r="K32" s="9" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>비용 처리</t>
+          <t>최종 점검</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>인쇄비·기념품·다과·중식·회의비 등 정산 및 결재</t>
+          <t>전일 전체 세팅·리허설 점검 (회의실·자료·물품·동선 일괄 확인)</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
@@ -4390,7 +4353,7 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>8/6~8/14</t>
+          <t>8/4~8/4</t>
         </is>
       </c>
       <c r="E33" s="10" t="n"/>
@@ -4399,36 +4362,7 @@
       <c r="H33" s="10" t="n"/>
       <c r="I33" s="10" t="n"/>
       <c r="J33" s="9" t="n"/>
-      <c r="K33" s="9" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>최종 점검</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>전일 전체 세팅·리허설 점검 (회의실·자료·물품·동선 일괄 확인)</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>DW</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>8/4~8/4</t>
-        </is>
-      </c>
-      <c r="E34" s="10" t="n"/>
-      <c r="F34" s="10" t="n"/>
-      <c r="G34" s="10" t="n"/>
-      <c r="H34" s="10" t="n"/>
-      <c r="I34" s="10" t="n"/>
-      <c r="J34" s="9" t="n"/>
-      <c r="K34" s="10" t="n"/>
+      <c r="K33" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/워크숍.xlsx
+++ b/data/워크숍.xlsx
@@ -11,7 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="준비업무" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="물품준비" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="당일타임라인" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="간트차트" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="참석자" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="간트차트" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3461,6 +3462,527 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>직급</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>소속</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>DLR</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Dr. Andreas Huber</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Institute Director (연구소장)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>총괄</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>총괄 책임자</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>DLR</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Dr. Haisol Kim</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Research Associate (연구원)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>1세부</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>DLR</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Dr. Klaus Peter Geigle</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Head of Department (부서장)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2세부</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>DLR</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Dr. Rémi Costa</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Group lead (그룹장)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3세부</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>DLR</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Dr. Michael Lang</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Senior Researcher (연구원)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3세부 대행</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>KIMM</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>송동근</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>본부장</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>총괄</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>책임자</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>KIMM</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>김민국</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>실장</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2세부</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>책임자</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>KIMM</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>황정재</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>책임</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1세부</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>책임자</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>KIMM</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>배용균</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>선임</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3세부</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>책임자</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>KIMM</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>민경욱</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>선임</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4세부</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>책임자</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>KIMM</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>강도원</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>책임</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>총괄</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>실무자</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>KIMM</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>김재현</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>선임</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2세부</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>실무자</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>KIMM</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>박진영</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>선임</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3세부</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>실무자</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>KIMM</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>이원준</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>선임</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>참여연구원</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>KIMM</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>박순호</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>선임</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>참여연구원</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>KIMM</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>변호성</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>선임</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>참여연구원</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>KIMM</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>김영상</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>책임</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>참여연구원</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>KIMM</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>이동근</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>선임</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>참여연구원</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>KIMM</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>조주형</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>책임</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>참여연구원</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/data/워크숍.xlsx
+++ b/data/워크숍.xlsx
@@ -3462,7 +3462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3470,6 +3470,7 @@
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3498,6 +3499,11 @@
           <t>역할</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -3525,6 +3531,7 @@
           <t>총괄 책임자</t>
         </is>
       </c>
+      <c r="F2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3548,6 +3555,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3571,6 +3579,7 @@
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -3594,6 +3603,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -3617,6 +3627,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -3644,6 +3655,7 @@
           <t>책임자</t>
         </is>
       </c>
+      <c r="F7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -3671,6 +3683,11 @@
           <t>책임자</t>
         </is>
       </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>MK-Kim-hub</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -3698,6 +3715,7 @@
           <t>책임자</t>
         </is>
       </c>
+      <c r="F9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -3725,6 +3743,7 @@
           <t>책임자</t>
         </is>
       </c>
+      <c r="F10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -3752,6 +3771,7 @@
           <t>책임자</t>
         </is>
       </c>
+      <c r="F11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3779,6 +3799,7 @@
           <t>실무자</t>
         </is>
       </c>
+      <c r="F12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3806,6 +3827,7 @@
           <t>실무자</t>
         </is>
       </c>
+      <c r="F13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3833,6 +3855,7 @@
           <t>실무자</t>
         </is>
       </c>
+      <c r="F14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3856,6 +3879,7 @@
           <t>참여연구원</t>
         </is>
       </c>
+      <c r="F15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3879,6 +3903,7 @@
           <t>참여연구원</t>
         </is>
       </c>
+      <c r="F16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3902,6 +3927,7 @@
           <t>참여연구원</t>
         </is>
       </c>
+      <c r="F17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3925,6 +3951,7 @@
           <t>참여연구원</t>
         </is>
       </c>
+      <c r="F18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3948,6 +3975,7 @@
           <t>참여연구원</t>
         </is>
       </c>
+      <c r="F19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -3971,6 +3999,7 @@
           <t>참여연구원</t>
         </is>
       </c>
+      <c r="F20" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/워크숍.xlsx
+++ b/data/워크숍.xlsx
@@ -3715,7 +3715,11 @@
           <t>책임자</t>
         </is>
       </c>
-      <c r="F9" s="3" t="n"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>HwangJJ-KIMM</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
